--- a/results/zero_shot/deepseek/zero_shot_deepseek_v1.xlsx
+++ b/results/zero_shot/deepseek/zero_shot_deepseek_v1.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,47 +429,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Глава</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Вопрос</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Ответ</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Статья ТК РФ</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ссылка на источник</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ответ_DeepSeek_ZeroShot</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Была галлюцинация (да/нет)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -1081,7 +1093,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1130,7 +1142,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1184,7 +1196,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1229,7 +1241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1275,7 +1287,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1339,7 +1351,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1392,7 +1404,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1434,7 +1446,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1481,7 +1493,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1534,7 +1546,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1578,7 +1590,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1621,7 +1633,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1667,7 +1679,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1714,7 +1726,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1764,7 +1776,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1802,7 +1814,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1845,7 +1857,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1897,7 +1909,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1936,7 +1948,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1987,7 +1999,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2035,7 +2047,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -2080,7 +2092,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -2122,7 +2134,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2169,7 +2181,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2214,7 +2226,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2257,7 +2269,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2296,7 +2308,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2345,7 +2357,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2389,7 +2401,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2439,7 +2451,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2491,7 +2503,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2539,7 +2551,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2599,7 +2611,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2642,7 +2654,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2681,7 +2693,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2729,7 +2741,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2779,7 +2791,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2821,7 +2833,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2871,7 +2883,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2914,7 +2926,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2970,7 +2982,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -3013,7 +3025,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -3056,7 +3068,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -3112,7 +3124,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -3172,7 +3184,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -3209,7 +3221,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -3251,7 +3263,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -3301,7 +3313,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -3353,7 +3365,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -3412,7 +3424,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -3468,7 +3480,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -3518,7 +3530,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -3557,7 +3569,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -3601,7 +3613,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -3647,7 +3659,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3699,7 +3711,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3758,7 +3770,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -3813,7 +3825,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3854,7 +3866,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3908,7 +3920,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3952,7 +3964,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3997,7 +4009,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -4054,7 +4066,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -4101,7 +4113,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -4160,7 +4172,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -4212,7 +4224,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -4272,7 +4284,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -4317,7 +4329,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -4371,7 +4383,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -4422,7 +4434,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -4482,7 +4494,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -4529,7 +4541,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -4584,7 +4596,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -4634,7 +4646,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -4690,7 +4702,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -4735,7 +4747,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -4794,7 +4806,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -4853,7 +4865,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4905,7 +4917,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -4957,7 +4969,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -5001,7 +5013,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -5044,7 +5056,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -5087,7 +5099,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -5135,7 +5147,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -5185,7 +5197,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -5234,7 +5246,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -5290,7 +5302,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -5340,7 +5352,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -5383,7 +5395,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -5432,7 +5444,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -5489,7 +5501,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -5546,7 +5558,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -5598,7 +5610,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -5653,7 +5665,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -5704,7 +5716,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -5770,7 +5782,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -5825,7 +5837,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -5877,7 +5889,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -5916,7 +5928,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -5962,7 +5974,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -6008,7 +6020,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -6051,7 +6063,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -6099,7 +6111,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -6142,7 +6154,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -6184,7 +6196,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -6225,7 +6237,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -6267,7 +6279,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -6312,7 +6324,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -6375,7 +6387,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -6415,7 +6427,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -6464,7 +6476,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -6512,7 +6524,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -6555,7 +6567,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -6607,7 +6619,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -6652,7 +6664,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -6701,7 +6713,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -6744,7 +6756,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -6797,7 +6809,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -6841,7 +6853,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -6880,7 +6892,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -6926,7 +6938,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -6974,7 +6986,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -7030,7 +7042,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -7079,7 +7091,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -7118,7 +7130,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -7160,7 +7172,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -7206,7 +7218,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -7252,7 +7264,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -7294,7 +7306,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -7333,7 +7345,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -7380,7 +7392,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -7419,7 +7431,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -7463,7 +7475,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -7518,7 +7530,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -7579,7 +7591,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -7631,7 +7643,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -7682,7 +7694,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -7724,7 +7736,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -7776,7 +7788,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -7821,7 +7833,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -7867,7 +7879,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -7913,7 +7925,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -7958,7 +7970,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -8000,7 +8012,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -8055,7 +8067,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -8102,7 +8114,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -8164,7 +8176,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -8230,7 +8242,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -8285,7 +8297,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -8335,7 +8347,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -8381,7 +8393,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -8434,7 +8446,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -8481,7 +8493,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -8530,7 +8542,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -8578,7 +8590,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -8633,7 +8645,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -8686,7 +8698,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -8736,7 +8748,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -8781,7 +8793,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -8840,7 +8852,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -8885,7 +8897,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -8930,7 +8942,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -8985,7 +8997,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -9037,7 +9049,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -9097,7 +9109,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -9153,7 +9165,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -9197,7 +9209,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -9240,7 +9252,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -9284,7 +9296,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -9348,7 +9360,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -9408,7 +9420,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -9447,7 +9459,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -9500,7 +9512,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -9546,7 +9558,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -9592,7 +9604,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -9631,7 +9643,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -9670,7 +9682,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -9722,7 +9734,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -9763,7 +9775,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -9808,7 +9820,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -9849,7 +9861,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -9903,7 +9915,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -9957,7 +9969,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -10010,7 +10022,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -10062,7 +10074,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -10106,7 +10118,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -10150,7 +10162,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -10196,7 +10208,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -10244,7 +10256,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -10293,7 +10305,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -10345,7 +10357,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -10387,7 +10399,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -10446,7 +10458,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -10515,7 +10527,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -10562,7 +10574,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -10609,7 +10621,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -10673,7 +10685,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -10716,7 +10728,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -10765,7 +10777,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -10813,7 +10825,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
